--- a/Bailey_Tincher_Resume.xlsx
+++ b/Bailey_Tincher_Resume.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bt/code/portfolio-gatsby/static/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21F294E-80D6-8B43-A713-7DB9B2B194C2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F0DF36-E39C-D945-B2AA-3609E80394AC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>AWS Backend Developer</t>
-  </si>
-  <si>
-    <t>https://adsa.cs.illinois.edu</t>
   </si>
   <si>
     <t>Integrated a full stack voice app in under 12 weeks that simplified the filing process of 40k+ claims/day, pitched the concept to a corporate executive, and sought out risk management and security teams to bring it near production</t>
@@ -301,6 +298,9 @@
   <si>
     <t>Created a machine learning model data refresh and quality assurance framework for our production trading systems</t>
   </si>
+  <si>
+    <t>https://aida.acm.illinois.edu</t>
+  </si>
 </sst>
 </file>
 
@@ -516,35 +516,38 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -555,17 +558,14 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -899,7 +899,7 @@
   <sheetData>
     <row r="1" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
@@ -927,11 +927,11 @@
       <c r="Y1" s="2"/>
     </row>
     <row r="2" spans="1:25" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
-        <v>16</v>
+      <c r="A2" s="37" t="s">
+        <v>15</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -956,9 +956,9 @@
       <c r="Y2" s="6"/>
     </row>
     <row r="3" spans="1:25" s="13" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -983,11 +983,11 @@
       <c r="Y3" s="6"/>
     </row>
     <row r="4" spans="1:25" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -1012,12 +1012,12 @@
       <c r="Y4" s="6"/>
     </row>
     <row r="5" spans="1:25" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -1047,7 +1047,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
@@ -1080,7 +1080,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="6"/>
@@ -1110,10 +1110,10 @@
       <c r="A8" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>22</v>
+      <c r="B8" s="27" t="s">
+        <v>21</v>
       </c>
-      <c r="C8" s="38"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17"/>
@@ -1165,11 +1165,11 @@
       <c r="Y9" s="6"/>
     </row>
     <row r="10" spans="1:25" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28" t="s">
-        <v>17</v>
+      <c r="A10" s="35" t="s">
+        <v>16</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
@@ -1197,17 +1197,17 @@
       <c r="A11" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="31" t="s">
-        <v>23</v>
+      <c r="B11" s="40" t="s">
+        <v>22</v>
       </c>
-      <c r="C11" s="31"/>
+      <c r="C11" s="40"/>
     </row>
     <row r="12" spans="1:25" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="20" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="22"/>
@@ -1238,7 +1238,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="22"/>
@@ -1292,11 +1292,11 @@
       <c r="Y14" s="22"/>
     </row>
     <row r="15" spans="1:25" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -1321,12 +1321,12 @@
       <c r="Y15" s="6"/>
     </row>
     <row r="16" spans="1:25" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26" t="s">
-        <v>35</v>
+      <c r="A16" s="33" t="s">
+        <v>34</v>
       </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="41" t="s">
-        <v>40</v>
+      <c r="B16" s="33"/>
+      <c r="C16" s="25" t="s">
+        <v>39</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1352,12 +1352,12 @@
       <c r="Y16" s="6"/>
     </row>
     <row r="17" spans="1:25" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="33" t="s">
-        <v>36</v>
+      <c r="A17" s="28" t="s">
+        <v>35</v>
       </c>
-      <c r="B17" s="30"/>
+      <c r="B17" s="29"/>
       <c r="C17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -1386,10 +1386,10 @@
       <c r="A18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>37</v>
+      <c r="B18" s="26" t="s">
+        <v>36</v>
       </c>
-      <c r="C18" s="25"/>
+      <c r="C18" s="26"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -1417,10 +1417,10 @@
       <c r="A19" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="25" t="s">
-        <v>38</v>
+      <c r="B19" s="26" t="s">
+        <v>37</v>
       </c>
-      <c r="C19" s="25"/>
+      <c r="C19" s="26"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
@@ -1448,10 +1448,10 @@
       <c r="A20" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="25" t="s">
-        <v>39</v>
+      <c r="B20" s="26" t="s">
+        <v>38</v>
       </c>
-      <c r="C20" s="25"/>
+      <c r="C20" s="26"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
@@ -1503,12 +1503,12 @@
       <c r="Y21" s="6"/>
     </row>
     <row r="22" spans="1:25" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="26" t="s">
-        <v>24</v>
+      <c r="A22" s="33" t="s">
+        <v>23</v>
       </c>
-      <c r="B22" s="26"/>
+      <c r="B22" s="33"/>
       <c r="C22" s="23" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -1534,10 +1534,10 @@
       <c r="Y22" s="6"/>
     </row>
     <row r="23" spans="1:25" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="33" t="s">
-        <v>25</v>
+      <c r="A23" s="28" t="s">
+        <v>24</v>
       </c>
-      <c r="B23" s="30"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="1" t="s">
         <v>1</v>
       </c>
@@ -1568,10 +1568,10 @@
       <c r="A24" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="25" t="s">
-        <v>26</v>
+      <c r="B24" s="26" t="s">
+        <v>25</v>
       </c>
-      <c r="C24" s="25"/>
+      <c r="C24" s="26"/>
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
@@ -1597,8 +1597,8 @@
     </row>
     <row r="25" spans="1:25" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -1626,10 +1626,10 @@
       <c r="A26" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="25" t="s">
-        <v>19</v>
+      <c r="B26" s="26" t="s">
+        <v>18</v>
       </c>
-      <c r="C26" s="25"/>
+      <c r="C26" s="26"/>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
@@ -1681,10 +1681,10 @@
       <c r="Y27" s="2"/>
     </row>
     <row r="28" spans="1:25" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="26"/>
+      <c r="B28" s="33"/>
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
@@ -1712,12 +1712,12 @@
       <c r="Y28" s="6"/>
     </row>
     <row r="29" spans="1:25" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="33" t="s">
+      <c r="A29" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="30"/>
+      <c r="B29" s="29"/>
       <c r="C29" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -1746,10 +1746,10 @@
       <c r="A30" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="25"/>
+      <c r="C30" s="26"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -1777,10 +1777,10 @@
       <c r="A31" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="25" t="s">
-        <v>41</v>
+      <c r="B31" s="26" t="s">
+        <v>40</v>
       </c>
-      <c r="C31" s="25"/>
+      <c r="C31" s="26"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -1832,11 +1832,11 @@
       <c r="Y32" s="6"/>
     </row>
     <row r="33" spans="1:25" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
@@ -1861,12 +1861,12 @@
       <c r="Y33" s="6"/>
     </row>
     <row r="34" spans="1:25" s="13" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29" t="s">
-        <v>28</v>
+      <c r="A34" s="41" t="s">
+        <v>27</v>
       </c>
-      <c r="B34" s="29"/>
+      <c r="B34" s="41"/>
       <c r="C34" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -1892,12 +1892,12 @@
       <c r="Y34" s="6"/>
     </row>
     <row r="35" spans="1:25" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="33" t="s">
+      <c r="A35" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="29"/>
+      <c r="C35" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -1926,10 +1926,10 @@
       <c r="A36" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="25" t="s">
-        <v>45</v>
+      <c r="B36" s="26" t="s">
+        <v>44</v>
       </c>
-      <c r="C36" s="25"/>
+      <c r="C36" s="26"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -1957,8 +1957,8 @@
       <c r="A37" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="27" t="s">
-        <v>49</v>
+      <c r="B37" s="31" t="s">
+        <v>48</v>
       </c>
       <c r="C37" s="32"/>
       <c r="D37" s="6"/>
@@ -2039,12 +2039,12 @@
       <c r="Y39" s="6"/>
     </row>
     <row r="40" spans="1:25" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="26" t="s">
-        <v>27</v>
+      <c r="A40" s="33" t="s">
+        <v>26</v>
       </c>
-      <c r="B40" s="26"/>
+      <c r="B40" s="33"/>
       <c r="C40" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -2070,12 +2070,12 @@
       <c r="Y40" s="6"/>
     </row>
     <row r="41" spans="1:25" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="33" t="s">
-        <v>30</v>
+      <c r="A41" s="28" t="s">
+        <v>29</v>
       </c>
-      <c r="B41" s="30"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
@@ -2104,19 +2104,19 @@
       <c r="A42" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="38" t="s">
-        <v>50</v>
+      <c r="B42" s="27" t="s">
+        <v>49</v>
       </c>
-      <c r="C42" s="38"/>
+      <c r="C42" s="27"/>
     </row>
     <row r="43" spans="1:25" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="25" t="s">
-        <v>33</v>
+      <c r="B43" s="26" t="s">
+        <v>32</v>
       </c>
-      <c r="C43" s="25"/>
+      <c r="C43" s="26"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
@@ -2144,10 +2144,10 @@
       <c r="A44" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B44" s="25" t="s">
-        <v>34</v>
+      <c r="B44" s="26" t="s">
+        <v>33</v>
       </c>
-      <c r="C44" s="25"/>
+      <c r="C44" s="26"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -2199,10 +2199,10 @@
       <c r="Y45" s="6"/>
     </row>
     <row r="46" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="40" t="s">
-        <v>29</v>
+      <c r="A46" s="30" t="s">
+        <v>28</v>
       </c>
-      <c r="B46" s="40"/>
+      <c r="B46" s="30"/>
       <c r="C46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2230,10 +2230,10 @@
       <c r="Y46" s="2"/>
     </row>
     <row r="47" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="33" t="s">
-        <v>30</v>
+      <c r="A47" s="28" t="s">
+        <v>29</v>
       </c>
-      <c r="B47" s="30"/>
+      <c r="B47" s="29"/>
       <c r="C47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2264,10 +2264,10 @@
       <c r="A48" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="25"/>
+      <c r="C48" s="26"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -2293,8 +2293,8 @@
     </row>
     <row r="49" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="24"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -2322,8 +2322,8 @@
       <c r="A50" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="27" t="s">
-        <v>14</v>
+      <c r="B50" s="31" t="s">
+        <v>13</v>
       </c>
       <c r="C50" s="32"/>
       <c r="D50" s="2"/>
@@ -27633,28 +27633,23 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A2:C3"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="B48:C49"/>
     <mergeCell ref="B50:C51"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A2:C3"/>
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B37:C38"/>
     <mergeCell ref="A41:B41"/>
@@ -27664,6 +27659,11 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B24:C25"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A28:B28"/>
